--- a/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/IO_ONLY/RWD_DP_PYRAD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.71 ± 0.09</t>
+          <t>0.75 ± 0.09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.60 ± 0.06</t>
+          <t>0.61 ± 0.10</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.45 ± 0.09</t>
+          <t>0.52 ± 0.11</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.87 ± 0.06</t>
+          <t>0.80 ± 0.11</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,12 +498,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.39 ± 0.21</t>
+          <t>0.39 ± 0.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.35 ± 0.22</t>
+          <t>0.45 ± 0.22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
